--- a/rcads/data/xls/03m_ActivityMethods.xlsx
+++ b/rcads/data/xls/03m_ActivityMethods.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_03m_ActivityMethods"/>
   </sheets>
   <definedNames>
-    <definedName name="_03m_ActivityMethods">'_03m_ActivityMethods'!$A$1:$C$181</definedName>
+    <definedName name="_03m_ActivityMethods">'_03m_ActivityMethods'!$A$1:$C$198</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -2337,6 +2337,187 @@
         <v>3</v>
       </c>
     </row>
+    <row outlineLevel="0" r="182">
+      <c r="A182" s="0">
+        <v>182</v>
+      </c>
+      <c r="B182" s="0">
+        <v>118</v>
+      </c>
+      <c r="C182" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="183">
+      <c r="A183" s="0">
+        <v>183</v>
+      </c>
+      <c r="B183" s="0">
+        <v>124</v>
+      </c>
+      <c r="C183" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="184">
+      <c r="A184" s="0">
+        <v>184</v>
+      </c>
+      <c r="B184" s="0">
+        <v>124</v>
+      </c>
+      <c r="C184" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="185">
+      <c r="A185" s="0">
+        <v>185</v>
+      </c>
+      <c r="B185" s="0">
+        <v>124</v>
+      </c>
+      <c r="C185" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="186">
+      <c r="A186" s="0">
+        <v>186</v>
+      </c>
+      <c r="B186" s="0">
+        <v>123</v>
+      </c>
+      <c r="C186" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="187">
+      <c r="A187" s="0">
+        <v>187</v>
+      </c>
+      <c r="B187" s="0">
+        <v>123</v>
+      </c>
+      <c r="C187" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="188">
+      <c r="A188" s="0">
+        <v>188</v>
+      </c>
+      <c r="B188" s="0">
+        <v>123</v>
+      </c>
+      <c r="C188" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="189">
+      <c r="A189" s="0">
+        <v>189</v>
+      </c>
+      <c r="B189" s="0">
+        <v>125</v>
+      </c>
+      <c r="C189" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="190">
+      <c r="A190" s="0">
+        <v>190</v>
+      </c>
+      <c r="B190" s="0">
+        <v>125</v>
+      </c>
+      <c r="C190" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="191">
+      <c r="A191" s="0">
+        <v>191</v>
+      </c>
+      <c r="B191" s="0">
+        <v>126</v>
+      </c>
+      <c r="C191" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="192">
+      <c r="A192" s="0">
+        <v>192</v>
+      </c>
+      <c r="B192" s="0">
+        <v>126</v>
+      </c>
+      <c r="C192" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="193">
+      <c r="A193" s="0">
+        <v>193</v>
+      </c>
+      <c r="B193" s="0">
+        <v>127</v>
+      </c>
+      <c r="C193" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="194">
+      <c r="A194" s="0">
+        <v>194</v>
+      </c>
+      <c r="B194" s="0">
+        <v>127</v>
+      </c>
+      <c r="C194" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="195">
+      <c r="A195" s="0">
+        <v>195</v>
+      </c>
+      <c r="B195" s="0">
+        <v>127</v>
+      </c>
+      <c r="C195" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="196">
+      <c r="A196" s="0">
+        <v>196</v>
+      </c>
+      <c r="B196" s="0">
+        <v>128</v>
+      </c>
+      <c r="C196" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="197">
+      <c r="A197" s="0">
+        <v>197</v>
+      </c>
+      <c r="B197" s="0">
+        <v>128</v>
+      </c>
+      <c r="C197" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="198">
+      <c r="A198" s="0">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
